--- a/AAII_Financials/Yearly/CTHR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CTHR_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/CTHR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CTHR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>CTHR</t>
   </si>
@@ -739,7 +739,7 @@
         <v>32200</v>
       </c>
       <c r="I8" s="3">
-        <v>13200</v>
+        <v>27900</v>
       </c>
       <c r="J8" s="3">
         <v>27000</v>
@@ -781,10 +781,10 @@
         <v>17000</v>
       </c>
       <c r="I9" s="3">
-        <v>8300</v>
+        <v>16200</v>
       </c>
       <c r="J9" s="3">
-        <v>15500</v>
+        <v>14900</v>
       </c>
       <c r="K9" s="3">
         <v>20400</v>
@@ -823,10 +823,10 @@
         <v>15300</v>
       </c>
       <c r="I10" s="3">
-        <v>4900</v>
+        <v>11800</v>
       </c>
       <c r="J10" s="3">
-        <v>11600</v>
+        <v>12200</v>
       </c>
       <c r="K10" s="3">
         <v>8800</v>
@@ -882,8 +882,8 @@
       <c r="H12" s="3">
         <v>0</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -967,10 +967,10 @@
         <v>400</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J14" s="3">
-        <v>-200</v>
+        <v>400</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>43900</v>
+        <v>37900</v>
       </c>
       <c r="E17" s="3">
-        <v>40200</v>
+        <v>40000</v>
       </c>
       <c r="F17" s="3">
-        <v>32800</v>
+        <v>33600</v>
       </c>
       <c r="G17" s="3">
-        <v>35500</v>
+        <v>29600</v>
       </c>
       <c r="H17" s="3">
-        <v>30000</v>
+        <v>29600</v>
       </c>
       <c r="I17" s="3">
-        <v>14800</v>
+        <v>28600</v>
       </c>
       <c r="J17" s="3">
-        <v>27500</v>
+        <v>27000</v>
       </c>
       <c r="K17" s="3">
         <v>33100</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-14000</v>
+        <v>-8000</v>
       </c>
       <c r="E18" s="3">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="F18" s="3">
-        <v>6500</v>
+        <v>5700</v>
       </c>
       <c r="G18" s="3">
-        <v>-6300</v>
+        <v>-500</v>
       </c>
       <c r="H18" s="3">
-        <v>2300</v>
+        <v>2700</v>
       </c>
       <c r="I18" s="3">
-        <v>-1600</v>
+        <v>-700</v>
       </c>
       <c r="J18" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>-3900</v>
@@ -1152,8 +1152,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>300</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1170,8 +1170,8 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-13000</v>
+        <v>-7300</v>
       </c>
       <c r="E21" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F21" s="3">
-        <v>7100</v>
+        <v>6200</v>
       </c>
       <c r="G21" s="3">
-        <v>-5700</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="I21" s="3">
-        <v>-1400</v>
+        <v>-300</v>
       </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K21" s="3">
         <v>-3400</v>
@@ -1239,8 +1239,8 @@
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>2300</v>
       </c>
       <c r="I23" s="3">
-        <v>-1600</v>
+        <v>-1100</v>
       </c>
       <c r="J23" s="3">
         <v>-400</v>
@@ -1336,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>2300</v>
       </c>
       <c r="I26" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="J26" s="3">
         <v>-500</v>
@@ -1462,7 +1462,7 @@
         <v>2300</v>
       </c>
       <c r="I27" s="3">
-        <v>-1600</v>
+        <v>-800</v>
       </c>
       <c r="J27" s="3">
         <v>-500</v>
@@ -1530,23 +1530,23 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1656,8 +1656,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-300</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1674,8 +1674,8 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>2300</v>
       </c>
       <c r="I33" s="3">
-        <v>-1300</v>
+        <v>-800</v>
       </c>
       <c r="J33" s="3">
         <v>-500</v>
@@ -1798,7 +1798,7 @@
         <v>2300</v>
       </c>
       <c r="I35" s="3">
-        <v>-1300</v>
+        <v>-800</v>
       </c>
       <c r="J35" s="3">
         <v>-500</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>6700</v>
+        <v>300</v>
       </c>
       <c r="F45" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="G45" s="3">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="I45" s="3">
-        <v>900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1000</v>
+        <v>300</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>700</v>
@@ -2159,26 +2159,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2373,10 +2373,10 @@
         <v>19300</v>
       </c>
       <c r="E52" s="3">
-        <v>28400</v>
+        <v>22500</v>
       </c>
       <c r="F52" s="3">
-        <v>24100</v>
+        <v>17800</v>
       </c>
       <c r="G52" s="3">
         <v>23200</v>
@@ -2573,26 +2573,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2300</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>2800</v>
+        <v>800</v>
       </c>
       <c r="G59" s="3">
-        <v>2500</v>
+        <v>800</v>
       </c>
       <c r="H59" s="3">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="I59" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>600</v>
@@ -2700,16 +2700,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G61" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2741,17 +2741,17 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2800</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>200</v>
@@ -3452,7 +3452,7 @@
         <v>2300</v>
       </c>
       <c r="I81" s="3">
-        <v>-1300</v>
+        <v>-800</v>
       </c>
       <c r="J81" s="3">
         <v>-500</v>
@@ -3497,7 +3497,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>500</v>
@@ -3512,7 +3512,7 @@
         <v>500</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>400</v>
@@ -4177,11 +4177,11 @@
       <c r="H100" s="3">
         <v>9100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -4204,26 +4204,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
